--- a/sheets/조재수대금교본/검수/10월의 어느 멋진날의.xlsx
+++ b/sheets/조재수대금교본/검수/10월의 어느 멋진날의.xlsx
@@ -4123,8 +4123,7 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -4169,8 +4168,7 @@
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M7" s="23"/>
@@ -4197,9 +4195,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-ㅂ
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C8" s="24"/>
@@ -4209,19 +4205,11 @@
         </is>
       </c>
       <c r="E8" s="24"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="24"/>
       <c r="H8" s="21"/>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
@@ -4230,28 +4218,18 @@
         </is>
       </c>
       <c r="M8" s="24"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="24"/>
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R8" s="21"/>
       <c r="S8" s="24"/>
     </row>
     <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應ㅂ
-ﾉ
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -4270,8 +4248,7 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -4297,7 +4274,7 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ㄴ</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
@@ -4331,7 +4308,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應ㅅ</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -4497,8 +4474,7 @@
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="C14" s="24"/>
@@ -4509,35 +4485,15 @@
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/10월의 어느 멋진날의.xlsx
+++ b/sheets/조재수대금교본/검수/10월의 어느 멋진날의.xlsx
@@ -4195,7 +4195,8 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰
+ㅂ</t>
         </is>
       </c>
       <c r="C8" s="24"/>
@@ -4229,7 +4230,8 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應</t>
+          <t xml:space="preserve">應ㅂ
+ﾉ</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -4274,7 +4276,7 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲ㄴ</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
@@ -4308,7 +4310,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應</t>
+          <t xml:space="preserve">應ㅅ</t>
         </is>
       </c>
       <c r="I10" s="23"/>

--- a/sheets/조재수대금교본/검수/10월의 어느 멋진날의.xlsx
+++ b/sheets/조재수대금교본/검수/10월의 어느 멋진날의.xlsx
@@ -3852,30 +3852,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="106.4" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="106.4" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="106.4" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="S5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="106.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="106.4" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="S7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="106.4" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="106.4" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="106.4" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="S10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="106.4" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="106.4" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="106.4" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="106.4" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4518,6 +4518,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>